--- a/excels/2급_기출문제_분개.xlsx
+++ b/excels/2급_기출문제_분개.xlsx
@@ -1,21 +1,20 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet name="문제" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="정답및해설" sheetId="2" state="visible" r:id="rId2"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties">
+  <Application>Microsoft Excel Compatible / Openpyxl 3.1.5</Application>
+  <AppVersion>3.1</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:creator>openpyxl</dc:creator>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-08-24T04:39:54Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-08-24T04:39:57Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="1">
@@ -125,7 +124,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -408,7 +407,23 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet name="문제" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="정답및해설" sheetId="2" state="visible" r:id="rId2"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3339,7 +3354,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3424,7 +3439,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>광고선전비</t>
+          <t>광고선전비(판)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3559,7 +3574,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>수선비</t>
+          <t>수선비(판)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3593,7 +3608,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>수수료비용</t>
+          <t>수수료비용(판)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3664,7 +3679,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>소모품비</t>
+          <t>소모품비(판)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3729,7 +3744,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>임차료</t>
+          <t>임차료(판)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3763,7 +3778,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>대손상각비</t>
+          <t>대손상각비(판)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3838,7 +3853,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>세금과공과</t>
+          <t>세금과공과(판)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4003,7 +4018,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4040,7 +4055,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>차량유지비</t>
+          <t>차량유지비(판)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4116,7 +4131,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>보험료</t>
+          <t>보험료(판)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4171,7 +4186,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>대손상각비</t>
+          <t>대손상각비(판)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4213,7 +4228,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>수선비</t>
+          <t>수선비(판)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4245,7 +4260,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>세금과공과</t>
+          <t>세금과공과(판)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4379,7 +4394,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(판)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4531,7 +4546,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>소모품비</t>
+          <t>소모품비(판)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4586,7 +4601,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>감가상각비</t>
+          <t>감가상각비(판)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4838,7 +4853,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4875,7 +4890,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>세금과공과</t>
+          <t>세금과공과(판)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5099,7 +5114,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>광고선전비</t>
+          <t>광고선전비(판)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5311,7 +5326,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>임차료</t>
+          <t>임차료(판)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5345,7 +5360,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>운반비</t>
+          <t>운반비(판)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5377,7 +5392,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>소모품비</t>
+          <t>소모품비(판)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5623,7 +5638,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>수수료비용</t>
+          <t>수수료비용(판)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5660,7 +5675,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(판)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5692,7 +5707,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5799,7 +5814,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>보험료</t>
+          <t>보험료(판)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5822,7 +5837,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>대손상각비</t>
+          <t>대손상각비(판)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6096,7 +6111,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>차량유지비</t>
+          <t>차량유지비(판)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6225,7 +6240,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>감가상각비</t>
+          <t>감가상각비(판)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6296,7 +6311,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>세금과공과</t>
+          <t>세금과공과(판)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6484,7 +6499,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>차량유지비</t>
+          <t>차량유지비(판)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6625,7 +6640,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>보험료</t>
+          <t>보험료(판)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6723,7 +6738,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>광고선전비</t>
+          <t>광고선전비(판)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6939,7 +6954,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>수수료비용</t>
+          <t>수수료비용(판)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6976,7 +6991,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7077,7 +7092,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>감가상각비</t>
+          <t>감가상각비(판)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7180,7 +7195,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>세금과공과</t>
+          <t>세금과공과(판)</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7433,7 +7448,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>보험료</t>
+          <t>보험료(판)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7488,7 +7503,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>대손상각비</t>
+          <t>대손상각비(판)</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">

--- a/excels/2급_기출문제_분개.xlsx
+++ b/excels/2급_기출문제_분개.xlsx
@@ -1,20 +1,21 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties">
-  <Application>Microsoft Excel Compatible / Openpyxl 3.1.5</Application>
-  <AppVersion>3.1</AppVersion>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet name="문제" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="정답및해설" sheetId="2" state="visible" r:id="rId2"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <dc:creator>openpyxl</dc:creator>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-08-24T04:39:54Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-08-24T04:39:57Z</dcterms:modified>
-</cp:coreProperties>
-</file>
-
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="1">
@@ -124,7 +125,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -407,23 +408,7 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet name="문제" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="정답및해설" sheetId="2" state="visible" r:id="rId2"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3354,7 +3339,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
